--- a/artfynd/A 26223-2024 artfynd.xlsx
+++ b/artfynd/A 26223-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1400,6 +1400,116 @@
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>118822335</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90464</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5445</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ekticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fomitiporia robusta</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Hällarna, Kilen, Oskarshamn, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>588066</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6350839</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Oskarshamn</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-07-31</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jan Brenander</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jan Brenander, Anneli Brenander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 26223-2024 artfynd.xlsx
+++ b/artfynd/A 26223-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118702443</v>
+        <v>118703016</v>
       </c>
       <c r="B2" t="n">
-        <v>57306</v>
+        <v>109751</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>219677</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>588182</v>
+        <v>587988</v>
       </c>
       <c r="R2" t="n">
-        <v>6350938</v>
+        <v>6350731</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -781,6 +773,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -921,10 +914,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118702454</v>
+        <v>118702694</v>
       </c>
       <c r="B4" t="n">
-        <v>90524</v>
+        <v>100107</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,34 +926,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -968,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588170</v>
+        <v>588027</v>
       </c>
       <c r="R4" t="n">
-        <v>6350929</v>
+        <v>6350834</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1014,6 +1004,11 @@
       <c r="AB4" t="inlineStr">
         <is>
           <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,7 +1036,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118702694</v>
+        <v>118702717</v>
       </c>
       <c r="B5" t="n">
         <v>100107</v>
@@ -1085,10 +1080,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588027</v>
+        <v>588056</v>
       </c>
       <c r="R5" t="n">
-        <v>6350834</v>
+        <v>6350842</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1156,17 +1151,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anneli Brenander, Jan Brenander</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118703016</v>
+        <v>118702454</v>
       </c>
       <c r="B6" t="n">
-        <v>109751</v>
+        <v>90524</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,31 +1170,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219677</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1207,10 +1205,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>587988</v>
+        <v>588170</v>
       </c>
       <c r="R6" t="n">
-        <v>6350731</v>
+        <v>6350929</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1280,10 +1278,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118702717</v>
+        <v>118702443</v>
       </c>
       <c r="B7" t="n">
-        <v>100107</v>
+        <v>57306</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1292,31 +1290,39 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1324,10 +1330,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588056</v>
+        <v>588182</v>
       </c>
       <c r="R7" t="n">
-        <v>6350842</v>
+        <v>6350938</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1372,18 +1378,12 @@
           <t>11:30</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1395,7 +1395,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anneli Brenander, Jan Brenander</t>
+          <t>Jan Brenander, Anneli Brenander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>

--- a/artfynd/A 26223-2024 artfynd.xlsx
+++ b/artfynd/A 26223-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118703016</v>
+        <v>118702443</v>
       </c>
       <c r="B2" t="n">
-        <v>109751</v>
+        <v>57306</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,31 +687,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219677</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>permanent revir</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +727,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587988</v>
+        <v>588182</v>
       </c>
       <c r="R2" t="n">
-        <v>6350731</v>
+        <v>6350938</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -773,7 +781,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -792,7 +799,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118702473</v>
+        <v>118702717</v>
       </c>
       <c r="B3" t="n">
         <v>100107</v>
@@ -836,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588170</v>
+        <v>588056</v>
       </c>
       <c r="R3" t="n">
-        <v>6350929</v>
+        <v>6350842</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -1036,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118702717</v>
+        <v>118702454</v>
       </c>
       <c r="B5" t="n">
-        <v>100107</v>
+        <v>90524</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,31 +1055,34 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1080,10 +1090,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588056</v>
+        <v>588170</v>
       </c>
       <c r="R5" t="n">
-        <v>6350842</v>
+        <v>6350929</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1126,11 +1136,6 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1158,10 +1163,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118702454</v>
+        <v>118702473</v>
       </c>
       <c r="B6" t="n">
-        <v>90524</v>
+        <v>100107</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,34 +1175,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1251,6 +1253,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118702443</v>
+        <v>118703016</v>
       </c>
       <c r="B7" t="n">
-        <v>57306</v>
+        <v>109751</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,39 +1297,31 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>219677</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>permanent revir</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1330,10 +1329,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588182</v>
+        <v>587988</v>
       </c>
       <c r="R7" t="n">
-        <v>6350938</v>
+        <v>6350731</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1384,6 +1383,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 26223-2024 artfynd.xlsx
+++ b/artfynd/A 26223-2024 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118702717</v>
+        <v>118702473</v>
       </c>
       <c r="B3" t="n">
-        <v>100107</v>
+        <v>100114</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588056</v>
+        <v>588170</v>
       </c>
       <c r="R3" t="n">
-        <v>6350842</v>
+        <v>6350929</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -924,7 +924,7 @@
         <v>118702694</v>
       </c>
       <c r="B4" t="n">
-        <v>100107</v>
+        <v>100114</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1043,10 +1043,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118702454</v>
+        <v>118703016</v>
       </c>
       <c r="B5" t="n">
-        <v>90524</v>
+        <v>109758</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1055,34 +1055,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>219677</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1090,10 +1087,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>588170</v>
+        <v>587988</v>
       </c>
       <c r="R5" t="n">
-        <v>6350929</v>
+        <v>6350731</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1163,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118702473</v>
+        <v>118702454</v>
       </c>
       <c r="B6" t="n">
-        <v>100107</v>
+        <v>90531</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,31 +1172,34 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1253,11 +1253,6 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1285,10 +1280,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118703016</v>
+        <v>118702717</v>
       </c>
       <c r="B7" t="n">
-        <v>109751</v>
+        <v>100114</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1301,21 +1296,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219677</v>
+        <v>222498</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1329,10 +1324,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>587988</v>
+        <v>588056</v>
       </c>
       <c r="R7" t="n">
-        <v>6350731</v>
+        <v>6350842</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1375,6 +1370,11 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,7 +1405,7 @@
         <v>118822335</v>
       </c>
       <c r="B8" t="n">
-        <v>90464</v>
+        <v>90471</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 26223-2024 artfynd.xlsx
+++ b/artfynd/A 26223-2024 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118702473</v>
+        <v>118703016</v>
       </c>
       <c r="B3" t="n">
-        <v>100114</v>
+        <v>109758</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,21 +815,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>219677</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Murgröna</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hedera helix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -843,10 +843,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>588170</v>
+        <v>587988</v>
       </c>
       <c r="R3" t="n">
-        <v>6350929</v>
+        <v>6350731</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -889,11 +889,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -921,7 +916,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118702694</v>
+        <v>118702473</v>
       </c>
       <c r="B4" t="n">
         <v>100114</v>
@@ -965,10 +960,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>588027</v>
+        <v>588170</v>
       </c>
       <c r="R4" t="n">
-        <v>6350834</v>
+        <v>6350929</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1043,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118703016</v>
+        <v>118702717</v>
       </c>
       <c r="B5" t="n">
-        <v>109758</v>
+        <v>100114</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1059,21 +1054,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219677</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Murgröna</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hedera helix</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1087,10 +1082,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>587988</v>
+        <v>588056</v>
       </c>
       <c r="R5" t="n">
-        <v>6350731</v>
+        <v>6350842</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1133,6 +1128,11 @@
       <c r="AB5" t="inlineStr">
         <is>
           <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1160,10 +1160,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118702454</v>
+        <v>118702694</v>
       </c>
       <c r="B6" t="n">
-        <v>90531</v>
+        <v>100114</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1172,34 +1172,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>222498</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1207,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>588170</v>
+        <v>588027</v>
       </c>
       <c r="R6" t="n">
-        <v>6350929</v>
+        <v>6350834</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1253,6 +1250,11 @@
       <c r="AB6" t="inlineStr">
         <is>
           <t>11:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,10 +1282,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118702717</v>
+        <v>118702454</v>
       </c>
       <c r="B7" t="n">
-        <v>100114</v>
+        <v>90531</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1292,31 +1294,34 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1324,10 +1329,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>588056</v>
+        <v>588170</v>
       </c>
       <c r="R7" t="n">
-        <v>6350842</v>
+        <v>6350929</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1370,11 +1375,6 @@
       <c r="AB7" t="inlineStr">
         <is>
           <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Riklig förekomst</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 26223-2024 artfynd.xlsx
+++ b/artfynd/A 26223-2024 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>118702443</v>
       </c>
       <c r="B6" t="n">
-        <v>57308</v>
+        <v>57494</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 26223-2024 artfynd.xlsx
+++ b/artfynd/A 26223-2024 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>118702443</v>
       </c>
       <c r="B6" t="n">
-        <v>57494</v>
+        <v>57497</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 26223-2024 artfynd.xlsx
+++ b/artfynd/A 26223-2024 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>118702443</v>
       </c>
       <c r="B6" t="n">
-        <v>57497</v>
+        <v>57503</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 26223-2024 artfynd.xlsx
+++ b/artfynd/A 26223-2024 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>118702443</v>
       </c>
       <c r="B6" t="n">
-        <v>57503</v>
+        <v>57506</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 26223-2024 artfynd.xlsx
+++ b/artfynd/A 26223-2024 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>118702443</v>
       </c>
       <c r="B6" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
